--- a/code/cod_algorithm/c_01_sample_results_ICD.xlsx
+++ b/code/cod_algorithm/c_01_sample_results_ICD.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC101"/>
+  <dimension ref="A1:AF101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,35 +529,50 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
+          <t>MATCH_COUNT</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>MATCHED_KEYWORDS</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>PRIMARY_CLASS_LEVEL_3</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>SECONDARY_CLASS_LEVEL_3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
           <t>FINAL_CAUSE_ACCIDENTAL</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>FINAL_CAUSE_INTENTIONAL</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>MANUAL</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>FINAL_CAUSE</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>CLASS_LEVEL_1</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>CLASS_LEVEL_2</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>CLASS_LEVEL_3</t>
         </is>
@@ -625,44 +640,37 @@
       <c r="S2" t="b">
         <v>1</v>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>100</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W2" t="b">
-        <v>0</v>
-      </c>
-      <c r="X2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -743,31 +751,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
-      </c>
-      <c r="X3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>CANCER</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>CANCER</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
@@ -835,44 +854,37 @@
       <c r="S4" t="b">
         <v>1</v>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>100</v>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W4" t="b">
-        <v>0</v>
-      </c>
-      <c r="X4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="inlineStr">
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -940,44 +952,37 @@
       <c r="S5" t="b">
         <v>1</v>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>100</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W5" t="b">
-        <v>0</v>
-      </c>
-      <c r="X5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -1034,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
@@ -1047,7 +1052,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ALCOHOL</t>
+          <t>ACCIDENTAL</t>
         </is>
       </c>
       <c r="U6" t="n">
@@ -1058,31 +1063,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W6" t="b">
-        <v>1</v>
-      </c>
-      <c r="X6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="b">
-        <v>0</v>
+      <c r="W6" t="n">
+        <v>6</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>ACCIDENTAL | ALCOHOL | INTOXICATION | METHAMPHETAMINE | OVERDOSE | UNINTENTIONAL</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Other Accidental</t>
+        </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>Overdose | Other Accidental</t>
+        </is>
+      </c>
+      <c r="AA6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>OVERDOSE</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>External/Injury (Unnatural Death)</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Accidental</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>Overdose</t>
         </is>
@@ -1145,31 +1165,34 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
-      <c r="W7" t="b">
-        <v>0</v>
-      </c>
-      <c r="X7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="inlineStr">
         <is>
           <t>UNDETERMINED</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -1250,31 +1273,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W8" t="b">
-        <v>0</v>
-      </c>
-      <c r="X8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="inlineStr">
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>CARDIAC</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Cardiovascular Disease</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>CARDIOVASCULAR DISEASE</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>Cardiovascular Disease</t>
         </is>
@@ -1355,31 +1389,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W9" t="b">
-        <v>0</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="inlineStr">
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>CARDIAC</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Cardiovascular Disease</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>CARDIOVASCULAR DISEASE</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>Cardiovascular Disease</t>
         </is>
@@ -1442,31 +1487,34 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
-      <c r="W10" t="b">
-        <v>0</v>
-      </c>
-      <c r="X10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="inlineStr">
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="inlineStr">
         <is>
           <t>UNDETERMINED</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -1534,44 +1582,37 @@
       <c r="S11" t="b">
         <v>1</v>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U11" t="n">
-        <v>100</v>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W11" t="b">
-        <v>0</v>
-      </c>
-      <c r="X11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="inlineStr">
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -1652,31 +1693,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W12" t="b">
-        <v>0</v>
-      </c>
-      <c r="X12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="b">
-        <v>0</v>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>HEART | HEART DISEASE</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Cardiovascular Disease</t>
+        </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
+          <t>Cardiovascular Disease</t>
+        </is>
+      </c>
+      <c r="AA12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>CARDIOVASCULAR DISEASE</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>Cardiovascular Disease</t>
         </is>
@@ -1757,31 +1813,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W13" t="b">
-        <v>0</v>
-      </c>
-      <c r="X13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="b">
-        <v>0</v>
+      <c r="W13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>ACUTE RESPIRATORY FAILURE | RESPIRATORY FAILURE</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Respiratory Disease</t>
+        </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
+          <t>Respiratory Disease</t>
+        </is>
+      </c>
+      <c r="AA13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
           <t>RESPIRATORY DISEASE</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AF13" t="inlineStr">
         <is>
           <t>Respiratory Disease</t>
         </is>
@@ -1849,44 +1920,37 @@
       <c r="S14" t="b">
         <v>1</v>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U14" t="n">
-        <v>100</v>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W14" t="b">
-        <v>0</v>
-      </c>
-      <c r="X14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="inlineStr">
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AF14" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -1967,31 +2031,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W15" t="b">
-        <v>0</v>
-      </c>
-      <c r="X15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="inlineStr">
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>CANCER</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>CANCER</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AF15" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
@@ -2059,44 +2134,37 @@
       <c r="S16" t="b">
         <v>1</v>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U16" t="n">
-        <v>100</v>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W16" t="b">
-        <v>0</v>
-      </c>
-      <c r="X16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="inlineStr">
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AF16" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -2177,31 +2245,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W17" t="b">
-        <v>0</v>
-      </c>
-      <c r="X17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="inlineStr">
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>CARDIAC</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Cardiovascular Disease</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="inlineStr">
         <is>
           <t>CARDIOVASCULAR DISEASE</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AD17" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AE17" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AF17" t="inlineStr">
         <is>
           <t>Cardiovascular Disease</t>
         </is>
@@ -2269,44 +2348,37 @@
       <c r="S18" t="b">
         <v>1</v>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U18" t="n">
-        <v>100</v>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W18" t="b">
-        <v>0</v>
-      </c>
-      <c r="X18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="inlineStr">
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -2374,44 +2446,37 @@
       <c r="S19" t="b">
         <v>1</v>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U19" t="n">
-        <v>100</v>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W19" t="b">
-        <v>0</v>
-      </c>
-      <c r="X19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="inlineStr">
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AD19" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AF19" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -2492,31 +2557,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W20" t="b">
-        <v>0</v>
-      </c>
-      <c r="X20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="b">
-        <v>0</v>
+      <c r="W20" t="n">
+        <v>2</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>CEREBROVASCULAR | HYPERTENSION</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Neuropsychiatric Conditions</t>
+        </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
+          <t>Other Non-Communicable Disease</t>
+        </is>
+      </c>
+      <c r="AA20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
           <t>NEUROPSYCHIATRIC ILLNESS</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AF20" t="inlineStr">
         <is>
           <t>Neuropsychiatric Conditions</t>
         </is>
@@ -2584,44 +2664,37 @@
       <c r="S21" t="b">
         <v>1</v>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U21" t="n">
-        <v>100</v>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W21" t="b">
-        <v>0</v>
-      </c>
-      <c r="X21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="inlineStr">
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AF21" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -2702,31 +2775,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W22" t="b">
-        <v>0</v>
-      </c>
-      <c r="X22" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="b">
-        <v>0</v>
+      <c r="W22" t="n">
+        <v>3</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>CARDIOMYOPATHY | HEART | HEART FAILURE</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Cardiovascular Disease</t>
+        </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
+          <t>Cardiovascular Disease</t>
+        </is>
+      </c>
+      <c r="AA22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
           <t>CARDIOVASCULAR DISEASE</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AF22" t="inlineStr">
         <is>
           <t>Cardiovascular Disease</t>
         </is>
@@ -2807,31 +2895,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W23" t="b">
-        <v>0</v>
-      </c>
-      <c r="X23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="inlineStr">
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>ANEURYSM</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Other Non-Communicable Disease</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="inlineStr">
         <is>
           <t>NON-COMMUNICABLE DISEASE</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AF23" t="inlineStr">
         <is>
           <t>Other Non-Communicable Disease</t>
         </is>
@@ -2912,31 +3011,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W24" t="b">
-        <v>0</v>
-      </c>
-      <c r="X24" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="inlineStr">
+      <c r="W24" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" t="inlineStr">
         <is>
           <t>SUICIDE</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Suicide</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>SUICIDE</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
         <is>
           <t>External/Injury (Unnatural Death)</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>Intentional</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AF24" t="inlineStr">
         <is>
           <t>Suicide</t>
         </is>
@@ -3017,31 +3127,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W25" t="b">
-        <v>0</v>
-      </c>
-      <c r="X25" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="b">
-        <v>0</v>
+      <c r="W25" t="n">
+        <v>2</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>IDIOPATHIC PULMONARY FIBROSIS | PULMONARY FIBROSIS</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Respiratory Disease</t>
+        </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
+          <t>Respiratory Disease</t>
+        </is>
+      </c>
+      <c r="AA25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
           <t>RESPIRATORY DISEASE</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AD25" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
+      <c r="AF25" t="inlineStr">
         <is>
           <t>Respiratory Disease</t>
         </is>
@@ -3104,31 +3229,34 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
-      <c r="W26" t="b">
-        <v>0</v>
-      </c>
-      <c r="X26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="inlineStr">
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="inlineStr">
         <is>
           <t>UNDETERMINED</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AF26" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -3185,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="b">
         <v>0</v>
@@ -3198,7 +3326,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>ALCOHOL</t>
+          <t>ACCIDENTAL</t>
         </is>
       </c>
       <c r="U27" t="n">
@@ -3209,31 +3337,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W27" t="b">
-        <v>1</v>
-      </c>
-      <c r="X27" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="b">
-        <v>0</v>
+      <c r="W27" t="n">
+        <v>4</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>ACCIDENTAL | ALCOHOL | INTOXICATION | METHAMPHETAMINE</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Other Accidental</t>
+        </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
+          <t>Overdose</t>
+        </is>
+      </c>
+      <c r="AA27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
           <t>OVERDOSE</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>External/Injury (Unnatural Death)</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>Accidental</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AF27" t="inlineStr">
         <is>
           <t>Overdose</t>
         </is>
@@ -3301,44 +3444,37 @@
       <c r="S28" t="b">
         <v>1</v>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U28" t="n">
-        <v>100</v>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W28" t="b">
-        <v>0</v>
-      </c>
-      <c r="X28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="inlineStr">
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AE28" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
+      <c r="AF28" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -3380,7 +3516,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
@@ -3408,7 +3544,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>ACUTE RESPIRATORY FAILURE</t>
+          <t>CANCER</t>
         </is>
       </c>
       <c r="U29" t="n">
@@ -3419,33 +3555,48 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W29" t="b">
-        <v>0</v>
-      </c>
-      <c r="X29" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="b">
-        <v>0</v>
+      <c r="W29" t="n">
+        <v>4</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>CANCER | SEPSIS | ACUTE RESPIRATORY FAILURE | RESPIRATORY FAILURE</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
+          <t>Other Non-Communicable Disease | Respiratory Disease</t>
+        </is>
+      </c>
+      <c r="AA29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
           <t>RESPIRATORY DISEASE</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AD29" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AE29" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Respiratory Disease</t>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Cancer</t>
         </is>
       </c>
     </row>
@@ -3524,31 +3675,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W30" t="b">
-        <v>0</v>
-      </c>
-      <c r="X30" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="inlineStr">
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>LEUKEMIA</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="inlineStr">
         <is>
           <t>CANCER</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AF30" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
@@ -3629,31 +3791,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W31" t="b">
-        <v>1</v>
-      </c>
-      <c r="X31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="inlineStr">
+      <c r="W31" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>ACCIDENT</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Other Accidental</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="inlineStr">
         <is>
           <t>ACCIDENTAL</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AD31" t="inlineStr">
         <is>
           <t>External/Injury (Unnatural Death)</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AE31" t="inlineStr">
         <is>
           <t>Accidental</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
+      <c r="AF31" t="inlineStr">
         <is>
           <t>Other Accidental</t>
         </is>
@@ -3734,31 +3907,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W32" t="b">
-        <v>0</v>
-      </c>
-      <c r="X32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="inlineStr">
+      <c r="W32" t="n">
+        <v>1</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>CARCINOMA</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="inlineStr">
         <is>
           <t>CANCER</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AE32" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
+      <c r="AF32" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
@@ -3839,31 +4023,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W33" t="b">
-        <v>0</v>
-      </c>
-      <c r="X33" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="inlineStr">
+      <c r="W33" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>CARDIOMYOPATHY</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Cardiovascular Disease</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="inlineStr">
         <is>
           <t>CARDIOVASCULAR DISEASE</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AE33" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
+      <c r="AF33" t="inlineStr">
         <is>
           <t>Cardiovascular Disease</t>
         </is>
@@ -3926,31 +4121,34 @@
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
-      <c r="W34" t="b">
-        <v>0</v>
-      </c>
-      <c r="X34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="inlineStr">
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="inlineStr">
         <is>
           <t>UNDETERMINED</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AE34" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
+      <c r="AF34" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -4018,44 +4216,37 @@
       <c r="S35" t="b">
         <v>1</v>
       </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U35" t="n">
-        <v>100</v>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W35" t="b">
-        <v>0</v>
-      </c>
-      <c r="X35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="inlineStr">
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AE35" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
+      <c r="AF35" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -4136,31 +4327,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W36" t="b">
-        <v>0</v>
-      </c>
-      <c r="X36" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="inlineStr">
+      <c r="W36" t="n">
+        <v>1</v>
+      </c>
+      <c r="X36" t="inlineStr">
         <is>
           <t>CANCER</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>CANCER</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AE36" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
+      <c r="AF36" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
@@ -4241,31 +4443,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W37" t="b">
-        <v>0</v>
-      </c>
-      <c r="X37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="inlineStr">
+      <c r="W37" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" t="inlineStr">
         <is>
           <t>CANCER</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>CANCER</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AF37" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
@@ -4333,44 +4546,37 @@
       <c r="S38" t="b">
         <v>1</v>
       </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U38" t="n">
-        <v>100</v>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W38" t="b">
-        <v>0</v>
-      </c>
-      <c r="X38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="inlineStr">
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AD38" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AE38" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
+      <c r="AF38" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -4451,31 +4657,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W39" t="b">
-        <v>0</v>
-      </c>
-      <c r="X39" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="inlineStr">
+      <c r="W39" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>CARDIO</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Cardiovascular Disease</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="inlineStr">
         <is>
           <t>CARDIOVASCULAR DISEASE</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AD39" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
+      <c r="AE39" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
+      <c r="AF39" t="inlineStr">
         <is>
           <t>Cardiovascular Disease</t>
         </is>
@@ -4556,31 +4773,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W40" t="b">
-        <v>0</v>
-      </c>
-      <c r="X40" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="inlineStr">
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="inlineStr">
         <is>
           <t>CANCER</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>CANCER</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
+      <c r="AE40" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
+      <c r="AF40" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
@@ -4648,44 +4876,37 @@
       <c r="S41" t="b">
         <v>1</v>
       </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U41" t="n">
-        <v>100</v>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W41" t="b">
-        <v>0</v>
-      </c>
-      <c r="X41" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="inlineStr">
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AE41" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
+      <c r="AF41" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -4739,7 +4960,7 @@
         <v>1</v>
       </c>
       <c r="O42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P42" t="b">
         <v>0</v>
@@ -4766,31 +4987,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W42" t="b">
-        <v>0</v>
-      </c>
-      <c r="X42" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="inlineStr">
+      <c r="W42" t="n">
+        <v>1</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>HEPATITIS</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Other Communicable Disease</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="inlineStr">
         <is>
           <t>COMMUNICABLE DISEASE</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AD42" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AE42" t="inlineStr">
         <is>
           <t>Communicable Disease</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
+      <c r="AF42" t="inlineStr">
         <is>
           <t>Other Communicable Disease</t>
         </is>
@@ -4844,7 +5076,7 @@
         <v>1</v>
       </c>
       <c r="O43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P43" t="b">
         <v>0</v>
@@ -4871,31 +5103,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W43" t="b">
-        <v>0</v>
-      </c>
-      <c r="X43" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="inlineStr">
+      <c r="W43" t="n">
+        <v>1</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>HEPATITIS</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Other Communicable Disease</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="inlineStr">
         <is>
           <t>COMMUNICABLE DISEASE</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AD43" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AE43" t="inlineStr">
         <is>
           <t>Communicable Disease</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
+      <c r="AF43" t="inlineStr">
         <is>
           <t>Other Communicable Disease</t>
         </is>
@@ -4976,31 +5219,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W44" t="b">
-        <v>0</v>
-      </c>
-      <c r="X44" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="b">
-        <v>0</v>
+      <c r="W44" t="n">
+        <v>2</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>HEART | HEART FAILURE</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Cardiovascular Disease</t>
+        </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
+          <t>Cardiovascular Disease</t>
+        </is>
+      </c>
+      <c r="AA44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
           <t>CARDIOVASCULAR DISEASE</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AE44" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
+      <c r="AF44" t="inlineStr">
         <is>
           <t>Cardiovascular Disease</t>
         </is>
@@ -5068,44 +5326,37 @@
       <c r="S45" t="b">
         <v>0</v>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="inlineStr">
         <is>
           <t>UNDETERMINED</t>
         </is>
       </c>
-      <c r="U45" t="n">
-        <v>100</v>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W45" t="b">
-        <v>0</v>
-      </c>
-      <c r="X45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>UNDETERMINED</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AE45" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
+      <c r="AF45" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -5168,31 +5419,34 @@
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
-      <c r="W46" t="b">
-        <v>0</v>
-      </c>
-      <c r="X46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="inlineStr">
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="inlineStr">
         <is>
           <t>UNDETERMINED</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AE46" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
+      <c r="AF46" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -5260,44 +5514,37 @@
       <c r="S47" t="b">
         <v>1</v>
       </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U47" t="n">
-        <v>100</v>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W47" t="b">
-        <v>0</v>
-      </c>
-      <c r="X47" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="inlineStr">
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AD47" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AE47" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
+      <c r="AF47" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -5378,31 +5625,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W48" t="b">
-        <v>0</v>
-      </c>
-      <c r="X48" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="inlineStr">
+      <c r="W48" t="n">
+        <v>1</v>
+      </c>
+      <c r="X48" t="inlineStr">
         <is>
           <t>CANCER</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>CANCER</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AE48" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
+      <c r="AF48" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
@@ -5470,44 +5728,37 @@
       <c r="S49" t="b">
         <v>1</v>
       </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U49" t="n">
-        <v>100</v>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W49" t="b">
-        <v>0</v>
-      </c>
-      <c r="X49" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="inlineStr">
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AD49" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AE49" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
+      <c r="AF49" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -5588,31 +5839,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W50" t="b">
-        <v>1</v>
-      </c>
-      <c r="X50" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="inlineStr">
+      <c r="W50" t="n">
+        <v>1</v>
+      </c>
+      <c r="X50" t="inlineStr">
         <is>
           <t>ACCIDENTAL</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Other Accidental</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AB50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>ACCIDENTAL</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
         <is>
           <t>External/Injury (Unnatural Death)</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AE50" t="inlineStr">
         <is>
           <t>Accidental</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
+      <c r="AF50" t="inlineStr">
         <is>
           <t>Other Accidental</t>
         </is>
@@ -5693,31 +5955,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W51" t="b">
-        <v>0</v>
-      </c>
-      <c r="X51" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="inlineStr">
+      <c r="W51" t="n">
+        <v>1</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>LIVER DISEASE</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Other Non-Communicable Disease</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="inlineStr">
         <is>
           <t>NON-COMMUNICABLE DISEASE</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AD51" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AE51" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
+      <c r="AF51" t="inlineStr">
         <is>
           <t>Other Non-Communicable Disease</t>
         </is>
@@ -5787,7 +6060,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>CARCINOMA</t>
+          <t>SEPTICEMIA</t>
         </is>
       </c>
       <c r="U52" t="n">
@@ -5798,31 +6071,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W52" t="b">
-        <v>0</v>
-      </c>
-      <c r="X52" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="b">
-        <v>0</v>
+      <c r="W52" t="n">
+        <v>2</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>SEPTICEMIA | CARCINOMA</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Other Non-Communicable Disease</t>
+        </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="AA52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
           <t>CANCER</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AD52" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
+      <c r="AE52" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
+      <c r="AF52" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
@@ -5890,44 +6178,37 @@
       <c r="S53" t="b">
         <v>1</v>
       </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U53" t="n">
-        <v>100</v>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W53" t="b">
-        <v>0</v>
-      </c>
-      <c r="X53" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="inlineStr">
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AD53" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AE53" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
+      <c r="AF53" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -6008,31 +6289,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W54" t="b">
-        <v>0</v>
-      </c>
-      <c r="X54" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="inlineStr">
+      <c r="W54" t="n">
+        <v>1</v>
+      </c>
+      <c r="X54" t="inlineStr">
         <is>
           <t>CANCER</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>CANCER</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AE54" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
+      <c r="AF54" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
@@ -6100,44 +6392,37 @@
       <c r="S55" t="b">
         <v>1</v>
       </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U55" t="n">
-        <v>100</v>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W55" t="b">
-        <v>0</v>
-      </c>
-      <c r="X55" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="inlineStr">
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AD55" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
+      <c r="AE55" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
+      <c r="AF55" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -6218,31 +6503,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W56" t="b">
-        <v>0</v>
-      </c>
-      <c r="X56" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="b">
-        <v>0</v>
+      <c r="W56" t="n">
+        <v>2</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>MYOCARDIAL | MYOCARDIAL INFARCTION</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Cardiovascular Disease</t>
+        </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
+          <t>Cardiovascular Disease</t>
+        </is>
+      </c>
+      <c r="AA56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
           <t>CARDIOVASCULAR DISEASE</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AD56" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
+      <c r="AE56" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
+      <c r="AF56" t="inlineStr">
         <is>
           <t>Cardiovascular Disease</t>
         </is>
@@ -6310,44 +6610,37 @@
       <c r="S57" t="b">
         <v>1</v>
       </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U57" t="n">
-        <v>100</v>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W57" t="b">
-        <v>0</v>
-      </c>
-      <c r="X57" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z57" t="inlineStr">
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AD57" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
+      <c r="AE57" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
+      <c r="AF57" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -6415,44 +6708,37 @@
       <c r="S58" t="b">
         <v>0</v>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="inlineStr">
         <is>
           <t>UNDETERMINED</t>
         </is>
       </c>
-      <c r="U58" t="n">
-        <v>100</v>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W58" t="b">
-        <v>0</v>
-      </c>
-      <c r="X58" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y58" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>UNDETERMINED</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AD58" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
+      <c r="AE58" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
+      <c r="AF58" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -6520,44 +6806,37 @@
       <c r="S59" t="b">
         <v>1</v>
       </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>ILLNESS</t>
-        </is>
-      </c>
-      <c r="U59" t="n">
-        <v>100</v>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W59" t="b">
-        <v>0</v>
-      </c>
-      <c r="X59" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y59" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z59" t="inlineStr">
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AD59" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
+      <c r="AE59" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
+      <c r="AF59" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -6625,44 +6904,37 @@
       <c r="S60" t="b">
         <v>1</v>
       </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U60" t="n">
-        <v>100</v>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W60" t="b">
-        <v>0</v>
-      </c>
-      <c r="X60" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z60" t="inlineStr">
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AD60" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
+      <c r="AE60" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
+      <c r="AF60" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -6730,44 +7002,37 @@
       <c r="S61" t="b">
         <v>1</v>
       </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U61" t="n">
-        <v>100</v>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W61" t="b">
-        <v>0</v>
-      </c>
-      <c r="X61" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="inlineStr">
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AD61" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
+      <c r="AE61" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
+      <c r="AF61" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -6835,44 +7100,37 @@
       <c r="S62" t="b">
         <v>1</v>
       </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U62" t="n">
-        <v>100</v>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W62" t="b">
-        <v>0</v>
-      </c>
-      <c r="X62" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z62" t="inlineStr">
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AD62" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
+      <c r="AE62" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
+      <c r="AF62" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -6953,31 +7211,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W63" t="b">
-        <v>0</v>
-      </c>
-      <c r="X63" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z63" t="inlineStr">
+      <c r="W63" t="n">
+        <v>1</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>CARDIOPULMONARY</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Cardiovascular Disease</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="inlineStr">
         <is>
           <t>CARDIOVASCULAR DISEASE</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AD63" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
+      <c r="AE63" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
+      <c r="AF63" t="inlineStr">
         <is>
           <t>Cardiovascular Disease</t>
         </is>
@@ -7045,44 +7314,37 @@
       <c r="S64" t="b">
         <v>1</v>
       </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U64" t="n">
-        <v>100</v>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W64" t="b">
-        <v>0</v>
-      </c>
-      <c r="X64" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z64" t="inlineStr">
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AD64" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
+      <c r="AE64" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
+      <c r="AF64" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -7152,7 +7414,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>ATHEROSCLEROTIC</t>
+          <t>CONGESTIVE HEART</t>
         </is>
       </c>
       <c r="U65" t="n">
@@ -7163,31 +7425,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W65" t="b">
-        <v>0</v>
-      </c>
-      <c r="X65" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y65" t="b">
-        <v>0</v>
+      <c r="W65" t="n">
+        <v>5</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>CONGESTIVE HEART | HEART | HEART FAILURE | ATHEROSCLEROTIC | CARDIOVASCULAR</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Cardiovascular Disease</t>
+        </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
+          <t>Cardiovascular Disease</t>
+        </is>
+      </c>
+      <c r="AA65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
           <t>CARDIOVASCULAR DISEASE</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AD65" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
+      <c r="AE65" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
+      <c r="AF65" t="inlineStr">
         <is>
           <t>Cardiovascular Disease</t>
         </is>
@@ -7257,7 +7534,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>HANGING</t>
+          <t>SUICIDE</t>
         </is>
       </c>
       <c r="U66" t="n">
@@ -7268,31 +7545,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W66" t="b">
-        <v>0</v>
-      </c>
-      <c r="X66" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y66" t="b">
-        <v>0</v>
+      <c r="W66" t="n">
+        <v>2</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>SUICIDE | HANGING</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>Suicide</t>
+        </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
+          <t>Suicide</t>
+        </is>
+      </c>
+      <c r="AA66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
           <t>SUICIDE</t>
         </is>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AD66" t="inlineStr">
         <is>
           <t>External/Injury (Unnatural Death)</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
+      <c r="AE66" t="inlineStr">
         <is>
           <t>Intentional</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
+      <c r="AF66" t="inlineStr">
         <is>
           <t>Suicide</t>
         </is>
@@ -7360,44 +7652,37 @@
       <c r="S67" t="b">
         <v>1</v>
       </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U67" t="n">
-        <v>100</v>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W67" t="b">
-        <v>0</v>
-      </c>
-      <c r="X67" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y67" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z67" t="inlineStr">
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA67" t="inlineStr">
+      <c r="AD67" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
+      <c r="AE67" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
+      <c r="AF67" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -7465,44 +7750,37 @@
       <c r="S68" t="b">
         <v>0</v>
       </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="U68" t="n">
-        <v>100</v>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W68" t="b">
-        <v>0</v>
-      </c>
-      <c r="X68" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y68" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z68" t="inlineStr">
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="inlineStr">
         <is>
           <t>UNDETERMINED</t>
         </is>
       </c>
-      <c r="AA68" t="inlineStr">
+      <c r="AD68" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
+      <c r="AE68" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
+      <c r="AF68" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -7573,31 +7851,34 @@
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
-      <c r="W69" t="b">
-        <v>0</v>
-      </c>
-      <c r="X69" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y69" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z69" t="inlineStr">
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="inlineStr">
         <is>
           <t>UNDETERMINED</t>
         </is>
       </c>
-      <c r="AA69" t="inlineStr">
+      <c r="AD69" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
+      <c r="AE69" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
+      <c r="AF69" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -7678,31 +7959,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W70" t="b">
-        <v>0</v>
-      </c>
-      <c r="X70" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y70" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z70" t="inlineStr">
+      <c r="W70" t="n">
+        <v>1</v>
+      </c>
+      <c r="X70" t="inlineStr">
         <is>
           <t>CANCER</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>CANCER</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
+      <c r="AE70" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
+      <c r="AF70" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
@@ -7783,31 +8075,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W71" t="b">
-        <v>0</v>
-      </c>
-      <c r="X71" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y71" t="b">
-        <v>0</v>
+      <c r="W71" t="n">
+        <v>3</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>LYMPHOMA | SEPSIS | RENAL FAILURE</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
+          <t>Other Non-Communicable Disease</t>
+        </is>
+      </c>
+      <c r="AA71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
           <t>CANCER</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AD71" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
+      <c r="AE71" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
+      <c r="AF71" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
@@ -7875,44 +8182,37 @@
       <c r="S72" t="b">
         <v>1</v>
       </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>ILLNESS</t>
-        </is>
-      </c>
-      <c r="U72" t="n">
-        <v>100</v>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W72" t="b">
-        <v>0</v>
-      </c>
-      <c r="X72" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y72" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z72" t="inlineStr">
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AD72" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
+      <c r="AE72" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
+      <c r="AF72" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -7980,44 +8280,37 @@
       <c r="S73" t="b">
         <v>1</v>
       </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U73" t="n">
-        <v>100</v>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W73" t="b">
-        <v>0</v>
-      </c>
-      <c r="X73" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y73" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z73" t="inlineStr">
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA73" t="inlineStr">
+      <c r="AD73" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
+      <c r="AE73" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
+      <c r="AF73" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -8087,7 +8380,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>HANGING</t>
+          <t>SUICIDE</t>
         </is>
       </c>
       <c r="U74" t="n">
@@ -8098,31 +8391,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W74" t="b">
-        <v>0</v>
-      </c>
-      <c r="X74" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y74" t="b">
-        <v>0</v>
+      <c r="W74" t="n">
+        <v>2</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>SUICIDE | HANGING</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Suicide</t>
+        </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
+          <t>Suicide</t>
+        </is>
+      </c>
+      <c r="AA74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
           <t>SUICIDE</t>
         </is>
       </c>
-      <c r="AA74" t="inlineStr">
+      <c r="AD74" t="inlineStr">
         <is>
           <t>External/Injury (Unnatural Death)</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
+      <c r="AE74" t="inlineStr">
         <is>
           <t>Intentional</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
+      <c r="AF74" t="inlineStr">
         <is>
           <t>Suicide</t>
         </is>
@@ -8185,31 +8493,34 @@
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
-      <c r="W75" t="b">
-        <v>0</v>
-      </c>
-      <c r="X75" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y75" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z75" t="inlineStr">
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="inlineStr">
         <is>
           <t>UNDETERMINED</t>
         </is>
       </c>
-      <c r="AA75" t="inlineStr">
+      <c r="AD75" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
+      <c r="AE75" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
+      <c r="AF75" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -8290,31 +8601,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W76" t="b">
-        <v>0</v>
-      </c>
-      <c r="X76" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y76" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z76" t="inlineStr">
+      <c r="W76" t="n">
+        <v>1</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>CARCINOMA</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="inlineStr">
         <is>
           <t>CANCER</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr">
+      <c r="AD76" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
+      <c r="AE76" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
+      <c r="AF76" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
@@ -8385,31 +8707,34 @@
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
-      <c r="W77" t="b">
-        <v>0</v>
-      </c>
-      <c r="X77" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y77" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z77" t="inlineStr">
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC77" t="inlineStr">
         <is>
           <t>UNDETERMINED</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AD77" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
+      <c r="AE77" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
+      <c r="AF77" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -8479,7 +8804,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>STAB</t>
+          <t>HOMICIDE</t>
         </is>
       </c>
       <c r="U78" t="n">
@@ -8490,31 +8815,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W78" t="b">
-        <v>0</v>
-      </c>
-      <c r="X78" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y78" t="b">
-        <v>0</v>
+      <c r="W78" t="n">
+        <v>2</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>HOMICIDE | STAB</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>Homicide</t>
+        </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
+          <t>Homicide</t>
+        </is>
+      </c>
+      <c r="AA78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB78" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
           <t>HOMICIDE</t>
         </is>
       </c>
-      <c r="AA78" t="inlineStr">
+      <c r="AD78" t="inlineStr">
         <is>
           <t>External/Injury (Unnatural Death)</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
+      <c r="AE78" t="inlineStr">
         <is>
           <t>Intentional</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
+      <c r="AF78" t="inlineStr">
         <is>
           <t>Homicide</t>
         </is>
@@ -8595,31 +8935,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W79" t="b">
-        <v>0</v>
-      </c>
-      <c r="X79" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y79" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z79" t="inlineStr">
+      <c r="W79" t="n">
+        <v>1</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>RESPIRATORY ARREST</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>Respiratory Disease</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC79" t="inlineStr">
         <is>
           <t>RESPIRATORY DISEASE</t>
         </is>
       </c>
-      <c r="AA79" t="inlineStr">
+      <c r="AD79" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
+      <c r="AE79" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
+      <c r="AF79" t="inlineStr">
         <is>
           <t>Respiratory Disease</t>
         </is>
@@ -8687,44 +9038,37 @@
       <c r="S80" t="b">
         <v>1</v>
       </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U80" t="n">
-        <v>100</v>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W80" t="b">
-        <v>0</v>
-      </c>
-      <c r="X80" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y80" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z80" t="inlineStr">
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC80" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA80" t="inlineStr">
+      <c r="AD80" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
+      <c r="AE80" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
+      <c r="AF80" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -8805,31 +9149,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W81" t="b">
-        <v>0</v>
-      </c>
-      <c r="X81" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y81" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z81" t="inlineStr">
+      <c r="W81" t="n">
+        <v>1</v>
+      </c>
+      <c r="X81" t="inlineStr">
         <is>
           <t>CANCER</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>CANCER</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
+      <c r="AE81" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
+      <c r="AF81" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
@@ -8883,7 +9238,7 @@
         <v>1</v>
       </c>
       <c r="O82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P82" t="b">
         <v>0</v>
@@ -8899,7 +9254,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>HEPATITIS</t>
+          <t>LIVER DISEASE</t>
         </is>
       </c>
       <c r="U82" t="n">
@@ -8910,31 +9265,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W82" t="b">
-        <v>0</v>
-      </c>
-      <c r="X82" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y82" t="b">
-        <v>0</v>
+      <c r="W82" t="n">
+        <v>2</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>LIVER DISEASE | HEPATITIS</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>Other Non-Communicable Disease</t>
+        </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
+          <t>Other Communicable Disease</t>
+        </is>
+      </c>
+      <c r="AA82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
           <t>COMMUNICABLE DISEASE</t>
         </is>
       </c>
-      <c r="AA82" t="inlineStr">
+      <c r="AD82" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
+      <c r="AE82" t="inlineStr">
         <is>
           <t>Communicable Disease</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
+      <c r="AF82" t="inlineStr">
         <is>
           <t>Other Communicable Disease</t>
         </is>
@@ -9015,31 +9385,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W83" t="b">
-        <v>0</v>
-      </c>
-      <c r="X83" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y83" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z83" t="inlineStr">
+      <c r="W83" t="n">
+        <v>1</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>CIRRHOSIS</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>Other Non-Communicable Disease</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC83" t="inlineStr">
         <is>
           <t>NON-COMMUNICABLE DISEASE</t>
         </is>
       </c>
-      <c r="AA83" t="inlineStr">
+      <c r="AD83" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
+      <c r="AE83" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
+      <c r="AF83" t="inlineStr">
         <is>
           <t>Other Non-Communicable Disease</t>
         </is>
@@ -9107,44 +9488,37 @@
       <c r="S84" t="b">
         <v>0</v>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC84" t="inlineStr">
         <is>
           <t>UNDETERMINED</t>
         </is>
       </c>
-      <c r="U84" t="n">
-        <v>100</v>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W84" t="b">
-        <v>0</v>
-      </c>
-      <c r="X84" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y84" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>UNDETERMINED</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
+      <c r="AD84" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
+      <c r="AE84" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
+      <c r="AF84" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -9225,31 +9599,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W85" t="b">
-        <v>0</v>
-      </c>
-      <c r="X85" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y85" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z85" t="inlineStr">
+      <c r="W85" t="n">
+        <v>1</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>CARDIAC</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>Cardiovascular Disease</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC85" t="inlineStr">
         <is>
           <t>CARDIOVASCULAR DISEASE</t>
         </is>
       </c>
-      <c r="AA85" t="inlineStr">
+      <c r="AD85" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
+      <c r="AE85" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
+      <c r="AF85" t="inlineStr">
         <is>
           <t>Cardiovascular Disease</t>
         </is>
@@ -9297,10 +9682,10 @@
         <v>0</v>
       </c>
       <c r="M86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" t="b">
         <v>1</v>
@@ -9319,7 +9704,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>RESPIRATORY FAILURE</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="U86" t="n">
@@ -9330,33 +9715,48 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W86" t="b">
-        <v>0</v>
-      </c>
-      <c r="X86" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y86" t="b">
-        <v>0</v>
+      <c r="W86" t="n">
+        <v>3</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>COVID-19 | RESPIRATORY FAILURE | INFECTION</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
+          <t>Respiratory Disease | Other Communicable Disease</t>
+        </is>
+      </c>
+      <c r="AA86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
           <t>RESPIRATORY DISEASE</t>
         </is>
       </c>
-      <c r="AA86" t="inlineStr">
+      <c r="AD86" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>Non-Communicable Disease</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Respiratory Disease</t>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>Communicable Disease</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
         </is>
       </c>
     </row>
@@ -9435,31 +9835,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W87" t="b">
-        <v>0</v>
-      </c>
-      <c r="X87" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y87" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z87" t="inlineStr">
+      <c r="W87" t="n">
+        <v>1</v>
+      </c>
+      <c r="X87" t="inlineStr">
         <is>
           <t>CANCER</t>
         </is>
       </c>
-      <c r="AA87" t="inlineStr">
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>CANCER</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
+      <c r="AE87" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
+      <c r="AF87" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
@@ -9527,44 +9938,37 @@
       <c r="S88" t="b">
         <v>1</v>
       </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U88" t="n">
-        <v>100</v>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W88" t="b">
-        <v>0</v>
-      </c>
-      <c r="X88" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y88" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z88" t="inlineStr">
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC88" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA88" t="inlineStr">
+      <c r="AD88" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
+      <c r="AE88" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
+      <c r="AF88" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -9632,44 +10036,37 @@
       <c r="S89" t="b">
         <v>1</v>
       </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U89" t="n">
-        <v>100</v>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W89" t="b">
-        <v>0</v>
-      </c>
-      <c r="X89" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y89" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z89" t="inlineStr">
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr"/>
+      <c r="AA89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC89" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA89" t="inlineStr">
+      <c r="AD89" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
+      <c r="AE89" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
+      <c r="AF89" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -9750,31 +10147,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W90" t="b">
-        <v>0</v>
-      </c>
-      <c r="X90" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y90" t="b">
-        <v>0</v>
+      <c r="W90" t="n">
+        <v>2</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>MYOCARDIAL | MYOCARDIAL INFARCTION</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Cardiovascular Disease</t>
+        </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
+          <t>Cardiovascular Disease</t>
+        </is>
+      </c>
+      <c r="AA90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
           <t>CARDIOVASCULAR DISEASE</t>
         </is>
       </c>
-      <c r="AA90" t="inlineStr">
+      <c r="AD90" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
+      <c r="AE90" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
+      <c r="AF90" t="inlineStr">
         <is>
           <t>Cardiovascular Disease</t>
         </is>
@@ -9828,7 +10240,7 @@
         <v>0</v>
       </c>
       <c r="O91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P91" t="b">
         <v>0</v>
@@ -9840,11 +10252,11 @@
         <v>1</v>
       </c>
       <c r="S91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>HANGING</t>
+          <t>SUICIDE</t>
         </is>
       </c>
       <c r="U91" t="n">
@@ -9855,31 +10267,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W91" t="b">
-        <v>0</v>
-      </c>
-      <c r="X91" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y91" t="b">
-        <v>0</v>
+      <c r="W91" t="n">
+        <v>4</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>SUICIDE | SUICIDE BY HANGING | HANGING | OBESITY</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>Suicide</t>
+        </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
+          <t>Suicide | Other Non-Communicable Disease</t>
+        </is>
+      </c>
+      <c r="AA91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB91" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
           <t>SUICIDE</t>
         </is>
       </c>
-      <c r="AA91" t="inlineStr">
+      <c r="AD91" t="inlineStr">
         <is>
           <t>External/Injury (Unnatural Death)</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
+      <c r="AE91" t="inlineStr">
         <is>
           <t>Intentional</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
+      <c r="AF91" t="inlineStr">
         <is>
           <t>Suicide</t>
         </is>
@@ -9960,31 +10387,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W92" t="b">
-        <v>0</v>
-      </c>
-      <c r="X92" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y92" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z92" t="inlineStr">
+      <c r="W92" t="n">
+        <v>1</v>
+      </c>
+      <c r="X92" t="inlineStr">
         <is>
           <t>SUICIDE</t>
         </is>
       </c>
-      <c r="AA92" t="inlineStr">
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>Suicide</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr"/>
+      <c r="AA92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB92" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>SUICIDE</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
         <is>
           <t>External/Injury (Unnatural Death)</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
+      <c r="AE92" t="inlineStr">
         <is>
           <t>Intentional</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
+      <c r="AF92" t="inlineStr">
         <is>
           <t>Suicide</t>
         </is>
@@ -10052,44 +10490,37 @@
       <c r="S93" t="b">
         <v>1</v>
       </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U93" t="n">
-        <v>100</v>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W93" t="b">
-        <v>0</v>
-      </c>
-      <c r="X93" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y93" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z93" t="inlineStr">
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" t="inlineStr"/>
+      <c r="Y93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr"/>
+      <c r="AA93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC93" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA93" t="inlineStr">
+      <c r="AD93" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
+      <c r="AE93" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
+      <c r="AF93" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -10170,31 +10601,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W94" t="b">
-        <v>0</v>
-      </c>
-      <c r="X94" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y94" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z94" t="inlineStr">
+      <c r="W94" t="n">
+        <v>1</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>MULTIPLE MYELOMA</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr"/>
+      <c r="AA94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC94" t="inlineStr">
         <is>
           <t>CANCER</t>
         </is>
       </c>
-      <c r="AA94" t="inlineStr">
+      <c r="AD94" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
+      <c r="AE94" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
+      <c r="AF94" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
@@ -10262,44 +10704,37 @@
       <c r="S95" t="b">
         <v>1</v>
       </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U95" t="n">
-        <v>100</v>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W95" t="b">
-        <v>0</v>
-      </c>
-      <c r="X95" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y95" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z95" t="inlineStr">
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr"/>
+      <c r="Z95" t="inlineStr"/>
+      <c r="AA95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC95" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA95" t="inlineStr">
+      <c r="AD95" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
+      <c r="AE95" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
+      <c r="AF95" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -10332,7 +10767,7 @@
         <v>1</v>
       </c>
       <c r="H96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" t="b">
         <v>0</v>
@@ -10369,7 +10804,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>HANGING</t>
+          <t>SUICIDE</t>
         </is>
       </c>
       <c r="U96" t="n">
@@ -10380,31 +10815,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W96" t="b">
-        <v>0</v>
-      </c>
-      <c r="X96" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y96" t="b">
-        <v>0</v>
+      <c r="W96" t="n">
+        <v>3</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>SUICIDE | HANGING | STRANGULATION</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>Suicide</t>
+        </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
+          <t>Suicide | Homicide</t>
+        </is>
+      </c>
+      <c r="AA96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB96" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
           <t>SUICIDE</t>
         </is>
       </c>
-      <c r="AA96" t="inlineStr">
+      <c r="AD96" t="inlineStr">
         <is>
           <t>External/Injury (Unnatural Death)</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
+      <c r="AE96" t="inlineStr">
         <is>
           <t>Intentional</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
+      <c r="AF96" t="inlineStr">
         <is>
           <t>Suicide</t>
         </is>
@@ -10472,44 +10922,37 @@
       <c r="S97" t="b">
         <v>1</v>
       </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>NATURAL</t>
-        </is>
-      </c>
-      <c r="U97" t="n">
-        <v>100</v>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W97" t="b">
-        <v>0</v>
-      </c>
-      <c r="X97" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y97" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z97" t="inlineStr">
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="n">
+        <v>0</v>
+      </c>
+      <c r="X97" t="inlineStr"/>
+      <c r="Y97" t="inlineStr"/>
+      <c r="Z97" t="inlineStr"/>
+      <c r="AA97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC97" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA97" t="inlineStr">
+      <c r="AD97" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
+      <c r="AE97" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
+      <c r="AF97" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -10590,31 +11033,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W98" t="b">
-        <v>0</v>
-      </c>
-      <c r="X98" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y98" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z98" t="inlineStr">
+      <c r="W98" t="n">
+        <v>1</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>RENAL FAILURE</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>Other Non-Communicable Disease</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr"/>
+      <c r="AA98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC98" t="inlineStr">
         <is>
           <t>NON-COMMUNICABLE DISEASE</t>
         </is>
       </c>
-      <c r="AA98" t="inlineStr">
+      <c r="AD98" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
+      <c r="AE98" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
+      <c r="AF98" t="inlineStr">
         <is>
           <t>Other Non-Communicable Disease</t>
         </is>
@@ -10695,31 +11149,42 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W99" t="b">
-        <v>0</v>
-      </c>
-      <c r="X99" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y99" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z99" t="inlineStr">
+      <c r="W99" t="n">
+        <v>1</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>CARCINOMA</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>Cancer</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC99" t="inlineStr">
         <is>
           <t>CANCER</t>
         </is>
       </c>
-      <c r="AA99" t="inlineStr">
+      <c r="AD99" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
+      <c r="AE99" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
+      <c r="AF99" t="inlineStr">
         <is>
           <t>Cancer</t>
         </is>
@@ -10787,44 +11252,37 @@
       <c r="S100" t="b">
         <v>1</v>
       </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>ILLNESS</t>
-        </is>
-      </c>
-      <c r="U100" t="n">
-        <v>100</v>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="W100" t="b">
-        <v>0</v>
-      </c>
-      <c r="X100" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y100" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z100" t="inlineStr">
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr"/>
+      <c r="AA100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC100" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="AA100" t="inlineStr">
+      <c r="AD100" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
+      <c r="AE100" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
+      <c r="AF100" t="inlineStr">
         <is>
           <t>Undetermined</t>
         </is>
@@ -10905,31 +11363,46 @@
           <t>Exact</t>
         </is>
       </c>
-      <c r="W101" t="b">
-        <v>0</v>
-      </c>
-      <c r="X101" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y101" t="b">
-        <v>0</v>
+      <c r="W101" t="n">
+        <v>2</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>CONGESTIVE HEART | HEART</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>Cardiovascular Disease</t>
+        </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
+          <t>Cardiovascular Disease</t>
+        </is>
+      </c>
+      <c r="AA101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
           <t>CARDIOVASCULAR DISEASE</t>
         </is>
       </c>
-      <c r="AA101" t="inlineStr">
+      <c r="AD101" t="inlineStr">
         <is>
           <t>Internal (Natural Death)</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
+      <c r="AE101" t="inlineStr">
         <is>
           <t>Non-Communicable Disease</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
+      <c r="AF101" t="inlineStr">
         <is>
           <t>Cardiovascular Disease</t>
         </is>
